--- a/research/traditional_assets/database/data/mexico/mexico_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_insurance_general.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.09669999999999999</v>
+        <v>0.0898</v>
       </c>
       <c r="E2">
-        <v>0.226</v>
+        <v>-0.08990000000000001</v>
       </c>
       <c r="G2">
-        <v>0.08041441952881068</v>
+        <v>0.0311640696608616</v>
       </c>
       <c r="H2">
-        <v>0.08041441952881068</v>
+        <v>0.0311640696608616</v>
       </c>
       <c r="I2">
-        <v>0.05268237297757593</v>
+        <v>0.032920867705469</v>
       </c>
       <c r="J2">
-        <v>0.03763475422011685</v>
+        <v>0.02477302783659951</v>
       </c>
       <c r="K2">
-        <v>119.8</v>
+        <v>82.7</v>
       </c>
       <c r="L2">
-        <v>0.03400510928186205</v>
+        <v>0.02105611569406253</v>
       </c>
       <c r="M2">
-        <v>138.8</v>
+        <v>62</v>
       </c>
       <c r="N2">
-        <v>0.1027159032043218</v>
+        <v>0.04619970193740686</v>
       </c>
       <c r="O2">
-        <v>1.158597662771286</v>
+        <v>0.7496977025392987</v>
       </c>
       <c r="P2">
-        <v>138.8</v>
+        <v>62</v>
       </c>
       <c r="Q2">
-        <v>0.1027159032043218</v>
+        <v>0.04619970193740686</v>
       </c>
       <c r="R2">
-        <v>1.158597662771286</v>
+        <v>0.7496977025392987</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>104.5</v>
+        <v>58.1</v>
       </c>
       <c r="V2">
-        <v>0.07733293865166876</v>
+        <v>0.04329359165424739</v>
       </c>
       <c r="W2">
-        <v>0.1397899649941657</v>
+        <v>0.09783508813439017</v>
       </c>
       <c r="X2">
-        <v>0.05515445461836581</v>
+        <v>0.09510532720756382</v>
       </c>
       <c r="Y2">
-        <v>0.08463551037579987</v>
+        <v>0.00272976092682635</v>
       </c>
       <c r="Z2">
-        <v>4.586642364275485</v>
+        <v>5.30183585313175</v>
       </c>
       <c r="AA2">
-        <v>0.1726171580750835</v>
+        <v>0.1313425271747141</v>
       </c>
       <c r="AB2">
-        <v>0.05515445461836581</v>
+        <v>0.09510532720756382</v>
       </c>
       <c r="AC2">
-        <v>0.1174627034567177</v>
+        <v>0.0362371999671503</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-104.5</v>
+        <v>-58.1</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -681,10 +681,10 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.08381456528713507</v>
+        <v>-0.04525274554092998</v>
       </c>
       <c r="AK2">
-        <v>-0.1410446753947901</v>
+        <v>-0.08512820512820513</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-0.5135135135135135</v>
+        <v>-0.407719298245614</v>
       </c>
     </row>
     <row r="3">
@@ -716,46 +716,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.09669999999999999</v>
+        <v>0.0898</v>
       </c>
       <c r="E3">
-        <v>0.226</v>
+        <v>-0.08990000000000001</v>
       </c>
       <c r="G3">
-        <v>0.08041441952881068</v>
+        <v>0.0311640696608616</v>
       </c>
       <c r="H3">
-        <v>0.08041441952881068</v>
+        <v>0.0311640696608616</v>
       </c>
       <c r="I3">
-        <v>0.05268237297757593</v>
+        <v>0.032920867705469</v>
       </c>
       <c r="J3">
-        <v>0.03763475422011685</v>
+        <v>0.02477302783659951</v>
       </c>
       <c r="K3">
-        <v>119.8</v>
+        <v>82.7</v>
       </c>
       <c r="L3">
-        <v>0.03400510928186205</v>
+        <v>0.02105611569406253</v>
       </c>
       <c r="M3">
-        <v>138.8</v>
+        <v>62</v>
       </c>
       <c r="N3">
-        <v>0.1027159032043218</v>
+        <v>0.04619970193740686</v>
       </c>
       <c r="O3">
-        <v>1.158597662771286</v>
+        <v>0.7496977025392987</v>
       </c>
       <c r="P3">
-        <v>138.8</v>
+        <v>62</v>
       </c>
       <c r="Q3">
-        <v>0.1027159032043218</v>
+        <v>0.04619970193740686</v>
       </c>
       <c r="R3">
-        <v>1.158597662771286</v>
+        <v>0.7496977025392987</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,31 +764,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>104.5</v>
+        <v>58.1</v>
       </c>
       <c r="V3">
-        <v>0.07733293865166876</v>
+        <v>0.04329359165424739</v>
       </c>
       <c r="W3">
-        <v>0.1397899649941657</v>
+        <v>0.09783508813439017</v>
       </c>
       <c r="X3">
-        <v>0.05515445461836581</v>
+        <v>0.09510532720756382</v>
       </c>
       <c r="Y3">
-        <v>0.08463551037579987</v>
+        <v>0.00272976092682635</v>
       </c>
       <c r="Z3">
-        <v>4.586642364275485</v>
+        <v>5.30183585313175</v>
       </c>
       <c r="AA3">
-        <v>0.1726171580750835</v>
+        <v>0.1313425271747141</v>
       </c>
       <c r="AB3">
-        <v>0.05515445461836581</v>
+        <v>0.09510532720756382</v>
       </c>
       <c r="AC3">
-        <v>0.1174627034567177</v>
+        <v>0.0362371999671503</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -800,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-104.5</v>
+        <v>-58.1</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -809,10 +809,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.08381456528713507</v>
+        <v>-0.04525274554092998</v>
       </c>
       <c r="AK3">
-        <v>-0.1410446753947901</v>
+        <v>-0.08512820512820513</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -824,7 +824,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.5135135135135135</v>
+        <v>-0.407719298245614</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/mexico/mexico_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_insurance_general.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0898</v>
+        <v>0.101</v>
       </c>
       <c r="E2">
-        <v>-0.08990000000000001</v>
+        <v>-0.0144</v>
       </c>
       <c r="G2">
-        <v>0.0311640696608616</v>
+        <v>0.05024645897870516</v>
       </c>
       <c r="H2">
-        <v>0.0311640696608616</v>
+        <v>0.05024645897870516</v>
       </c>
       <c r="I2">
-        <v>0.032920867705469</v>
+        <v>0.05731876010676642</v>
       </c>
       <c r="J2">
-        <v>0.02477302783659951</v>
+        <v>0.04258917175374854</v>
       </c>
       <c r="K2">
-        <v>82.7</v>
+        <v>191.7</v>
       </c>
       <c r="L2">
-        <v>0.02105611569406253</v>
+        <v>0.03734876380852183</v>
       </c>
       <c r="M2">
-        <v>62</v>
+        <v>121.9</v>
       </c>
       <c r="N2">
-        <v>0.04619970193740686</v>
+        <v>0.06579231433506046</v>
       </c>
       <c r="O2">
-        <v>0.7496977025392987</v>
+        <v>0.635889410537298</v>
       </c>
       <c r="P2">
-        <v>62</v>
+        <v>121.9</v>
       </c>
       <c r="Q2">
-        <v>0.04619970193740686</v>
+        <v>0.06579231433506046</v>
       </c>
       <c r="R2">
-        <v>0.7496977025392987</v>
+        <v>0.635889410537298</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>58.1</v>
+        <v>49.8</v>
       </c>
       <c r="V2">
-        <v>0.04329359165424739</v>
+        <v>0.02687823834196891</v>
       </c>
       <c r="W2">
-        <v>0.09783508813439017</v>
+        <v>0.2588441803942749</v>
       </c>
       <c r="X2">
-        <v>0.09510532720756382</v>
+        <v>0.08476757902921384</v>
       </c>
       <c r="Y2">
-        <v>0.00272976092682635</v>
+        <v>0.174076601365061</v>
       </c>
       <c r="Z2">
-        <v>5.30183585313175</v>
+        <v>7.52043956043956</v>
       </c>
       <c r="AA2">
-        <v>0.1313425271747141</v>
+        <v>0.3202892921032456</v>
       </c>
       <c r="AB2">
-        <v>0.09510532720756382</v>
+        <v>0.08476757902921384</v>
       </c>
       <c r="AC2">
-        <v>0.0362371999671503</v>
+        <v>0.2355217130740317</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-58.1</v>
+        <v>-49.8</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -681,10 +681,10 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.04525274554092998</v>
+        <v>-0.02762063227953411</v>
       </c>
       <c r="AK2">
-        <v>-0.08512820512820513</v>
+        <v>-0.06032707450030284</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-0.407719298245614</v>
+        <v>-0.1448516579406632</v>
       </c>
     </row>
     <row r="3">
@@ -716,46 +716,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0898</v>
+        <v>0.101</v>
       </c>
       <c r="E3">
-        <v>-0.08990000000000001</v>
+        <v>-0.0144</v>
       </c>
       <c r="G3">
-        <v>0.0311640696608616</v>
+        <v>0.05024645897870516</v>
       </c>
       <c r="H3">
-        <v>0.0311640696608616</v>
+        <v>0.05024645897870516</v>
       </c>
       <c r="I3">
-        <v>0.032920867705469</v>
+        <v>0.05731876010676642</v>
       </c>
       <c r="J3">
-        <v>0.02477302783659951</v>
+        <v>0.04258917175374854</v>
       </c>
       <c r="K3">
-        <v>82.7</v>
+        <v>191.7</v>
       </c>
       <c r="L3">
-        <v>0.02105611569406253</v>
+        <v>0.03734876380852183</v>
       </c>
       <c r="M3">
-        <v>62</v>
+        <v>121.9</v>
       </c>
       <c r="N3">
-        <v>0.04619970193740686</v>
+        <v>0.06579231433506046</v>
       </c>
       <c r="O3">
-        <v>0.7496977025392987</v>
+        <v>0.635889410537298</v>
       </c>
       <c r="P3">
-        <v>62</v>
+        <v>121.9</v>
       </c>
       <c r="Q3">
-        <v>0.04619970193740686</v>
+        <v>0.06579231433506046</v>
       </c>
       <c r="R3">
-        <v>0.7496977025392987</v>
+        <v>0.635889410537298</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,31 +764,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>58.1</v>
+        <v>49.8</v>
       </c>
       <c r="V3">
-        <v>0.04329359165424739</v>
+        <v>0.02687823834196891</v>
       </c>
       <c r="W3">
-        <v>0.09783508813439017</v>
+        <v>0.2588441803942749</v>
       </c>
       <c r="X3">
-        <v>0.09510532720756382</v>
+        <v>0.08476757902921384</v>
       </c>
       <c r="Y3">
-        <v>0.00272976092682635</v>
+        <v>0.174076601365061</v>
       </c>
       <c r="Z3">
-        <v>5.30183585313175</v>
+        <v>7.52043956043956</v>
       </c>
       <c r="AA3">
-        <v>0.1313425271747141</v>
+        <v>0.3202892921032456</v>
       </c>
       <c r="AB3">
-        <v>0.09510532720756382</v>
+        <v>0.08476757902921384</v>
       </c>
       <c r="AC3">
-        <v>0.0362371999671503</v>
+        <v>0.2355217130740317</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -800,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-58.1</v>
+        <v>-49.8</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -809,10 +809,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.04525274554092998</v>
+        <v>-0.02762063227953411</v>
       </c>
       <c r="AK3">
-        <v>-0.08512820512820513</v>
+        <v>-0.06032707450030284</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -824,7 +824,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.407719298245614</v>
+        <v>-0.1448516579406632</v>
       </c>
     </row>
   </sheetData>
